--- a/图片清单.xlsx
+++ b/图片清单.xlsx
@@ -424,16 +424,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G173"/>
+  <dimension ref="A1:F138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="34" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -459,17 +458,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>建议替换为（体育公园相关）</t>
+          <t>类型</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>优先级</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>文件名</t>
+          <t>替换文件名</t>
         </is>
       </c>
     </row>
@@ -490,15 +484,10 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>体育公园实景：城市新城航拍</t>
+          <t>网络照片</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
-        <is>
-          <t>建议换</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
         <is>
           <t>figs/user/s001.jpg</t>
         </is>
@@ -516,20 +505,15 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>草坪亲子活动（放风筝、野餐）</t>
+          <t>草坪放风筝·亲子活动</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>体育公园实景：草坪亲子活动（放风筝、野餐）</t>
+          <t>网络照片</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
-        <is>
-          <t>建议换</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
         <is>
           <t>figs/user/s002.jpg</t>
         </is>
@@ -551,20 +535,15 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>阳光草坪休闲人群</t>
+          <t>群众轮滑活动</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>体育公园实景：阳光草坪休闲人群</t>
+          <t>网络照片</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
-        <is>
-          <t>建议换</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
         <is>
           <t>figs/user/s003.jpg</t>
         </is>
@@ -577,29 +556,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>01 课题研究背景</t>
+          <t>1.1 前言</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>户外单杠健身器械</t>
+          <t>骑行活动人群</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>体育公园实景：户外单杠健身器械</t>
+          <t>网络照片</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
-        <is>
-          <t>建议换</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
         <is>
           <t>figs/user/s004.jpg</t>
         </is>
@@ -612,29 +586,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.1 前言</t>
+          <t>1.1 选题背景——时代需求</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>社区骑行活动人群</t>
+          <t>城市高架航拍</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>体育公园实景：社区骑行活动人群</t>
+          <t>网络照片</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
-        <is>
-          <t>建议换</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
         <is>
           <t>figs/user/s005.jpg</t>
         </is>
@@ -656,20 +625,15 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>公园道路航拍</t>
+          <t>篮球比赛</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>体育公园实景：公园道路航拍</t>
+          <t>网络照片</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
-        <is>
-          <t>建议换</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
         <is>
           <t>figs/user/s006.jpg</t>
         </is>
@@ -691,20 +655,15 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>篮球场比赛</t>
+          <t>行人与长椅老人</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>体育公园实景：篮球场比赛</t>
+          <t>网络照片</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
-        <is>
-          <t>建议换</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
         <is>
           <t>figs/user/s007.jpg</t>
         </is>
@@ -726,20 +685,15 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>老人聚坐聊天</t>
+          <t>体育场看台</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>体育公园实景：老人聚坐聊天</t>
+          <t>网络照片</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
-        <is>
-          <t>建议换</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
         <is>
           <t>figs/user/s008.jpg</t>
         </is>
@@ -752,29 +706,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.1 选题背景——时代需求</t>
+          <t>1.1 选题背景——政策导向</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>网球场打球</t>
+          <t>女子足球</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>体育公园实景：网球场打球</t>
+          <t>网络照片</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
-        <is>
-          <t>建议换</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
         <is>
           <t>figs/user/s009.jpg</t>
         </is>
@@ -787,29 +736,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.1 选题背景——政策导向</t>
+          <t>1.1 选题背景——人口结构与地方需求</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>网球运动员</t>
+          <t>人口构成柱状图</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>体育公园实景：网球运动员</t>
+          <t>项目图（不用换）</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
-        <is>
-          <t>建议换</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
         <is>
           <t>figs/user/s010.jpg</t>
         </is>
@@ -822,29 +766,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.1 选题背景——政策导向</t>
+          <t>1.1 选题背景——人口结构与地方需求</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>室内球馆（排球、羽毛球）</t>
+          <t>场地裸土空地</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>体育公园实景：室内球馆（排球、羽毛球）</t>
+          <t>项目图（不用换）</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
-        <is>
-          <t>建议换</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
         <is>
           <t>figs/user/s011.jpg</t>
         </is>
@@ -857,29 +796,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.1 选题背景——政策导向</t>
+          <t>1.1 选题背景——人口结构与地方需求</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>儿童在草坪游戏</t>
+          <t>场地原生林地</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>体育公园实景：儿童在草坪游戏</t>
+          <t>项目图（不用换）</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
-        <is>
-          <t>建议换</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
         <is>
           <t>figs/user/s012.jpg</t>
         </is>
@@ -892,25 +826,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.1 选题背景——人口结构与地方需求</t>
+          <t>1.2 研究目的</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>人口构成柱状图</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
+          <t>儿童草坪游戏</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>网络照片</t>
+        </is>
+      </c>
       <c r="F14" t="inlineStr">
-        <is>
-          <t>项目自有图，不用换</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
         <is>
           <t>figs/user/s013.jpg</t>
         </is>
@@ -923,25 +856,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.1 选题背景——人口结构与地方需求</t>
+          <t>1.2 研究目的</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>场地裸土空地照片</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
+          <t>公园长椅与草坪</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>网络照片</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr">
-        <is>
-          <t>项目自有图，不用换</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
         <is>
           <t>figs/user/s014.jpg</t>
         </is>
@@ -954,25 +886,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.1 选题背景——人口结构与地方需求</t>
+          <t>1.2 研究目的</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>场地原生林地照片</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
+          <t>丘陵地貌</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>网络照片</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr">
-        <is>
-          <t>项目自有图，不用换</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
         <is>
           <t>figs/user/s015.jpg</t>
         </is>
@@ -985,29 +916,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.2 研究目的</t>
+          <t>1.3 研究意义</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>大草坪人群活动</t>
+          <t>全龄人群抠图带</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>体育公园实景：大草坪人群活动</t>
+          <t>网络照片</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
-        <is>
-          <t>建议换</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
         <is>
           <t>figs/user/s016.jpg</t>
         </is>
@@ -1020,29 +946,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.2 研究目的</t>
+          <t>1.4 技术路线与研究方法</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>公园湖岸生态水景</t>
+          <t>技术路线图</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>体育公园实景：公园湖岸生态水景</t>
+          <t>项目图（不用换）</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
-        <is>
-          <t>建议换</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
         <is>
           <t>figs/user/s017.jpg</t>
         </is>
@@ -1055,29 +976,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.2 研究目的</t>
+          <t>1.5 相关概念</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>山地丘陵地貌</t>
+          <t>球场边观看</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>体育公园实景：山地丘陵地貌</t>
+          <t>网络照片</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
-        <is>
-          <t>建议换</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
         <is>
           <t>figs/user/s018.jpg</t>
         </is>
@@ -1090,29 +1006,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.3 研究意义</t>
+          <t>1.5 相关概念</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>各年龄人群抠图带</t>
+          <t>健身球训练</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>体育公园实景：各年龄人群抠图带</t>
+          <t>网络照片</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
-        <is>
-          <t>建议换</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
         <is>
           <t>figs/user/s019.jpg</t>
         </is>
@@ -1125,25 +1036,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.4 技术路线与研究方法</t>
+          <t>1.5 相关概念</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>技术路线图</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
+          <t>儿童秋千</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>网络照片</t>
+        </is>
+      </c>
       <c r="F21" t="inlineStr">
-        <is>
-          <t>项目自有图，不用换</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
         <is>
           <t>figs/user/s020.jpg</t>
         </is>
@@ -1156,29 +1066,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.5 相关概念</t>
+          <t>1.6 国内外研究现状</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>露天球场人群</t>
+          <t>室内球类运动</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>体育公园实景：露天球场人群</t>
+          <t>网络照片</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
-        <is>
-          <t>建议换</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
         <is>
           <t>figs/user/s021.jpg</t>
         </is>
@@ -1191,29 +1096,24 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.5 相关概念</t>
+          <t>1.6 国内外研究现状</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>体育场看台</t>
+          <t>极限运动场</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>体育公园实景：体育场看台</t>
+          <t>网络照片</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
-        <is>
-          <t>建议换</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
         <is>
           <t>figs/user/s022.jpg</t>
         </is>
@@ -1226,29 +1126,24 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1.5 相关概念</t>
+          <t>1.6 国内外研究现状</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>健身运动</t>
+          <t>街道骑行</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>体育公园实景：健身运动</t>
+          <t>网络照片</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
-        <is>
-          <t>建议换</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
         <is>
           <t>figs/user/s023.jpg</t>
         </is>
@@ -1261,29 +1156,24 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1.5 相关概念</t>
+          <t>1.6 国内外研究现状</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>轮椅运动、无障碍运动</t>
+          <t>滨水林荫长椅</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>体育公园实景：轮椅运动、无障碍运动</t>
+          <t>网络照片</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
-        <is>
-          <t>建议换</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
         <is>
           <t>figs/user/s024.jpg</t>
         </is>
@@ -1296,29 +1186,24 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1.5 相关概念</t>
+          <t>1.6 国内外研究现状——发展脉络</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>儿童秋千游乐设施</t>
+          <t>湖岸林地水景</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>体育公园实景：儿童秋千游乐设施</t>
+          <t>网络照片</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
-        <is>
-          <t>建议换</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
         <is>
           <t>figs/user/s025.jpg</t>
         </is>
@@ -1331,29 +1216,24 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1.5 相关概念</t>
+          <t>1.6 国内外研究现状——发展脉络</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>滨水林荫座椅</t>
+          <t>繁忙街道人流</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>体育公园实景：滨水林荫座椅</t>
+          <t>网络照片</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
-        <is>
-          <t>建议换</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
         <is>
           <t>figs/user/s026.jpg</t>
         </is>
@@ -1366,29 +1246,24 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1.6 国内外研究现状</t>
+          <t>1.6 国内外研究现状——发展脉络</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>少儿球类训练</t>
+          <t>户外单杠</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>体育公园实景：少儿球类训练</t>
+          <t>网络照片</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
-        <is>
-          <t>建议换</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
         <is>
           <t>figs/user/s027.jpg</t>
         </is>
@@ -1401,29 +1276,24 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1.6 国内外研究现状</t>
+          <t>1.6 国内外研究现状——发展脉络</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>滑板极限运动场</t>
+          <t>校园球场活动</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>体育公园实景：滑板极限运动场</t>
+          <t>网络照片</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
-        <is>
-          <t>建议换</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
         <is>
           <t>figs/user/s028.jpg</t>
         </is>
@@ -1436,29 +1306,24 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1.6 国内外研究现状</t>
+          <t>1.6 国内外研究现状——发展脉络</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>滑板少年</t>
+          <t>室内交谊活动</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>体育公园实景：滑板少年</t>
+          <t>网络照片</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
-        <is>
-          <t>建议换</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
         <is>
           <t>figs/user/s029.jpg</t>
         </is>
@@ -1471,29 +1336,24 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1.6 国内外研究现状</t>
+          <t>1.6 国内外研究现状——发展脉络</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>花境、野花组合</t>
+          <t>广场人群</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>体育公园实景：花境、野花组合</t>
+          <t>网络照片</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
-        <is>
-          <t>建议换</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
         <is>
           <t>figs/user/s030.jpg</t>
         </is>
@@ -1515,20 +1375,15 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>花卉植物景观</t>
+          <t>芜湖桥下体育公园案例</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>体育公园实景：花卉植物景观</t>
+          <t>项目图（不用换）</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
-        <is>
-          <t>建议换</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
         <is>
           <t>figs/user/s031.jpg</t>
         </is>
@@ -1550,20 +1405,15 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>城市广场入口</t>
+          <t>场地卫星影像</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>体育公园实景：城市广场入口</t>
+          <t>项目图（不用换）</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
-        <is>
-          <t>建议换</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
         <is>
           <t>figs/user/s032.jpg</t>
         </is>
@@ -1576,29 +1426,24 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1.6 国内外研究现状——发展脉络</t>
+          <t>1.7 案例参考（一）成都天府公园西区</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>山地骑行</t>
+          <t>成都天府公园西区案例</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>体育公园实景：山地骑行</t>
+          <t>项目图（不用换）</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
-        <is>
-          <t>建议换</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
         <is>
           <t>figs/user/s033.jpg</t>
         </is>
@@ -1611,29 +1456,24 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1.6 国内外研究现状——发展脉络</t>
+          <t>1.7 案例参考（一）成都天府公园西区</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>绿道骑行</t>
+          <t>成都天府公园西区案例</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>体育公园实景：绿道骑行</t>
+          <t>项目图（不用换）</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
-        <is>
-          <t>建议换</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
         <is>
           <t>figs/user/s034.jpg</t>
         </is>
@@ -1646,29 +1486,24 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1.6 国内外研究现状——发展脉络</t>
+          <t>1.7 案例参考（一）成都天府公园西区</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>网球场打球</t>
+          <t>成都天府公园西区案例</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>体育公园实景：网球场打球</t>
+          <t>项目图（不用换）</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
-        <is>
-          <t>必换（当前重复）</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
         <is>
           <t>figs/user/s035.jpg</t>
         </is>
@@ -1681,29 +1516,24 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1.6 国内外研究现状——发展脉络</t>
+          <t>1.7 案例参考（一）成都天府公园西区</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>花坛盆栽</t>
+          <t>成都天府公园西区案例</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>体育公园实景：花坛盆栽</t>
+          <t>项目图（不用换）</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
-        <is>
-          <t>建议换</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
         <is>
           <t>figs/user/s036.jpg</t>
         </is>
@@ -1716,25 +1546,24 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1.6 国内外研究现状——发展脉络</t>
+          <t>1.7 案例参考（一）成都天府公园西区</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>芜湖桥下体育公园案例照片</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
+          <t>成都天府公园西区案例</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>项目图（不用换）</t>
+        </is>
+      </c>
       <c r="F38" t="inlineStr">
-        <is>
-          <t>项目自有图，不用换</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
         <is>
           <t>figs/user/s037.jpg</t>
         </is>
@@ -1747,25 +1576,24 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1.6 国内外研究现状——发展脉络</t>
+          <t>1.7 案例参考（二）成都天府牧山活力体育公园</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>场地卫星影像</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
+          <t>成都牧山体育公园案例</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>项目图（不用换）</t>
+        </is>
+      </c>
       <c r="F39" t="inlineStr">
-        <is>
-          <t>项目自有图，不用换</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
         <is>
           <t>figs/user/s038.jpg</t>
         </is>
@@ -1778,25 +1606,24 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1.7 案例参考（一）成都天府公园西区</t>
+          <t>1.7 案例参考（二）成都天府牧山活力体育公园</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>成都天府公园西区案例照片</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
+          <t>成都牧山体育公园案例</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>项目图（不用换）</t>
+        </is>
+      </c>
       <c r="F40" t="inlineStr">
-        <is>
-          <t>项目自有图，不用换</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
         <is>
           <t>figs/user/s039.jpg</t>
         </is>
@@ -1809,25 +1636,24 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1.7 案例参考（一）成都天府公园西区</t>
+          <t>1.7 案例参考（二）成都天府牧山活力体育公园</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>成都天府公园西区案例照片</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr"/>
+          <t>成都牧山体育公园案例</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>项目图（不用换）</t>
+        </is>
+      </c>
       <c r="F41" t="inlineStr">
-        <is>
-          <t>项目自有图，不用换</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
         <is>
           <t>figs/user/s040.jpg</t>
         </is>
@@ -1840,25 +1666,24 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1.7 案例参考（一）成都天府公园西区</t>
+          <t>1.7 案例参考（二）成都天府牧山活力体育公园</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>成都天府公园西区案例照片</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr"/>
+          <t>成都牧山体育公园案例</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>项目图（不用换）</t>
+        </is>
+      </c>
       <c r="F42" t="inlineStr">
-        <is>
-          <t>项目自有图，不用换</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
         <is>
           <t>figs/user/s041.jpg</t>
         </is>
@@ -1871,25 +1696,24 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>1.7 案例参考（一）成都天府公园西区</t>
+          <t>1.7 案例参考（三）苏州相城活力体育公园</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>成都天府公园西区案例照片</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr"/>
+          <t>苏州相城体育公园案例</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>项目图（不用换）</t>
+        </is>
+      </c>
       <c r="F43" t="inlineStr">
-        <is>
-          <t>项目自有图，不用换</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
         <is>
           <t>figs/user/s042.jpg</t>
         </is>
@@ -1902,25 +1726,24 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>1.7 案例参考（一）成都天府公园西区</t>
+          <t>1.7 案例参考（三）苏州相城活力体育公园</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>成都天府公园西区案例照片</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr"/>
+          <t>苏州相城体育公园案例</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>项目图（不用换）</t>
+        </is>
+      </c>
       <c r="F44" t="inlineStr">
-        <is>
-          <t>项目自有图，不用换</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
         <is>
           <t>figs/user/s043.jpg</t>
         </is>
@@ -1933,25 +1756,24 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>1.7 案例参考（二）成都天府牧山活力体育公园</t>
+          <t>1.7 案例参考（三）苏州相城活力体育公园</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>成都牧山体育公园案例照片</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr"/>
+          <t>苏州相城体育公园案例</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>项目图（不用换）</t>
+        </is>
+      </c>
       <c r="F45" t="inlineStr">
-        <is>
-          <t>项目自有图，不用换</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
         <is>
           <t>figs/user/s044.jpg</t>
         </is>
@@ -1964,25 +1786,24 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>1.7 案例参考（二）成都天府牧山活力体育公园</t>
+          <t>1.7 案例参考（三）苏州相城活力体育公园</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>成都牧山体育公园案例照片</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr"/>
+          <t>苏州相城体育公园案例</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>项目图（不用换）</t>
+        </is>
+      </c>
       <c r="F46" t="inlineStr">
-        <is>
-          <t>项目自有图，不用换</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
         <is>
           <t>figs/user/s045.jpg</t>
         </is>
@@ -1995,25 +1816,24 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>1.7 案例参考（二）成都天府牧山活力体育公园</t>
+          <t>1.7 案例参考（四）芜湖长江三桥桥下体育公园</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>成都牧山体育公园案例照片</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr"/>
+          <t>芜湖桥下体育公园案例</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>项目图（不用换）</t>
+        </is>
+      </c>
       <c r="F47" t="inlineStr">
-        <is>
-          <t>项目自有图，不用换</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
         <is>
           <t>figs/user/s046.jpg</t>
         </is>
@@ -2026,25 +1846,24 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>1.7 案例参考（二）成都天府牧山活力体育公园</t>
+          <t>1.7 案例参考（四）芜湖长江三桥桥下体育公园</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>成都牧山体育公园案例照片</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr"/>
+          <t>芜湖桥下体育公园案例</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>项目图（不用换）</t>
+        </is>
+      </c>
       <c r="F48" t="inlineStr">
-        <is>
-          <t>项目自有图，不用换</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
         <is>
           <t>figs/user/s047.jpg</t>
         </is>
@@ -2057,25 +1876,24 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>1.7 案例参考（三）苏州相城活力体育公园</t>
+          <t>02 项目研究概述</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>苏州相城体育公园案例照片</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr"/>
+          <t>场地卫星影像</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>项目图（不用换）</t>
+        </is>
+      </c>
       <c r="F49" t="inlineStr">
-        <is>
-          <t>项目自有图，不用换</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
         <is>
           <t>figs/user/s048.jpg</t>
         </is>
@@ -2088,25 +1906,24 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>1.7 案例参考（三）苏州相城活力体育公园</t>
+          <t>2.1 上位规划</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>苏州相城体育公园案例照片</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr"/>
+          <t>场地现状地图</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>项目图（不用换）</t>
+        </is>
+      </c>
       <c r="F50" t="inlineStr">
-        <is>
-          <t>项目自有图，不用换</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
         <is>
           <t>figs/user/s049.jpg</t>
         </is>
@@ -2119,25 +1936,24 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>1.7 案例参考（三）苏州相城活力体育公园</t>
+          <t>2.1 上位规划</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>苏州相城体育公园案例照片</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr"/>
+          <t>场地卫星影像</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>项目图（不用换）</t>
+        </is>
+      </c>
       <c r="F51" t="inlineStr">
-        <is>
-          <t>项目自有图，不用换</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
         <is>
           <t>figs/user/s050.jpg</t>
         </is>
@@ -2150,25 +1966,24 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>1.7 案例参考（三）苏州相城活力体育公园</t>
+          <t>2.2 区位分析</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>苏州相城体育公园案例照片</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr"/>
+          <t>区位分析图</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>项目图（不用换）</t>
+        </is>
+      </c>
       <c r="F52" t="inlineStr">
-        <is>
-          <t>项目自有图，不用换</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
         <is>
           <t>figs/user/s051.jpg</t>
         </is>
@@ -2181,25 +1996,24 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>1.7 案例参考（四）芜湖长江三桥桥下体育公园</t>
+          <t>2.2 区位分析</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>芜湖桥下体育公园案例照片</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr"/>
+          <t>场地现状地图</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>项目图（不用换）</t>
+        </is>
+      </c>
       <c r="F53" t="inlineStr">
-        <is>
-          <t>项目自有图，不用换</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
         <is>
           <t>figs/user/s052.jpg</t>
         </is>
@@ -2212,25 +2026,24 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>1.7 案例参考（四）芜湖长江三桥桥下体育公园</t>
+          <t>2.3 气候分析——气温与降水</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>芜湖桥下体育公园案例照片</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr"/>
+          <t>气温分析图</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>项目图（不用换）</t>
+        </is>
+      </c>
       <c r="F54" t="inlineStr">
-        <is>
-          <t>项目自有图，不用换</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
         <is>
           <t>figs/user/s053.jpg</t>
         </is>
@@ -2243,25 +2056,24 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>02 项目研究概述</t>
+          <t>2.3 气候分析——气温与降水</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>场地卫星影像</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr"/>
+          <t>降水分析图</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>项目图（不用换）</t>
+        </is>
+      </c>
       <c r="F55" t="inlineStr">
-        <is>
-          <t>项目自有图，不用换</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
         <is>
           <t>figs/user/s054.jpg</t>
         </is>
@@ -2274,25 +2086,24 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>02 项目研究概述</t>
+          <t>2.3 气候分析——气温与降水</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>场地周边住宅照片</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr"/>
+          <t>草坪休闲人群</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>网络照片</t>
+        </is>
+      </c>
       <c r="F56" t="inlineStr">
-        <is>
-          <t>项目自有图，不用换</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
         <is>
           <t>figs/user/s055.jpg</t>
         </is>
@@ -2305,25 +2116,24 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2.1 上位规划</t>
+          <t>2.3 气候分析——日照、湿度与雨日</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>场地现状地图</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr"/>
+          <t>日照时数图</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>项目图（不用换）</t>
+        </is>
+      </c>
       <c r="F57" t="inlineStr">
-        <is>
-          <t>项目自有图，不用换</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
         <is>
           <t>figs/user/s056.jpg</t>
         </is>
@@ -2336,25 +2146,24 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2.1 上位规划</t>
+          <t>2.3 气候分析——日照、湿度与雨日</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>场地卫星影像</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr"/>
+          <t>湿度降水日数图</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>项目图（不用换）</t>
+        </is>
+      </c>
       <c r="F58" t="inlineStr">
-        <is>
-          <t>项目自有图，不用换</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
         <is>
           <t>figs/user/s057.jpg</t>
         </is>
@@ -2367,29 +2176,24 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2.1 上位规划</t>
+          <t>2.3 气候分析——日照、湿度与雨日</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>城市街道车流</t>
+          <t>温室植物景观</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>体育公园实景：城市街道车流</t>
+          <t>网络照片</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
-        <is>
-          <t>建议换</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
         <is>
           <t>figs/user/s058.jpg</t>
         </is>
@@ -2402,29 +2206,24 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2.1 上位规划</t>
+          <t>2.4 植物分析</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>林荫道路</t>
+          <t>植物配置分析图</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>体育公园实景：林荫道路</t>
+          <t>项目图（不用换）</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
-        <is>
-          <t>建议换</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
         <is>
           <t>figs/user/s059.jpg</t>
         </is>
@@ -2437,25 +2236,24 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2.2 区位分析</t>
+          <t>2.5 历史文化分析</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>区位分析图</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr"/>
+          <t>历史文化分析图</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>项目图（不用换）</t>
+        </is>
+      </c>
       <c r="F61" t="inlineStr">
-        <is>
-          <t>项目自有图，不用换</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
         <is>
           <t>figs/user/s060.jpg</t>
         </is>
@@ -2468,25 +2266,24 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2.2 区位分析</t>
+          <t>2.5 历史文化分析</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>场地现状地图</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr"/>
+          <t>街头市井生活</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>网络照片</t>
+        </is>
+      </c>
       <c r="F62" t="inlineStr">
-        <is>
-          <t>项目自有图，不用换</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
         <is>
           <t>figs/user/s061.jpg</t>
         </is>
@@ -2499,25 +2296,24 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2.3 气候分析——气温与降水</t>
+          <t>2.6 周边道路分析</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>气温分析图</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr"/>
+          <t>道路分析图</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>项目图（不用换）</t>
+        </is>
+      </c>
       <c r="F63" t="inlineStr">
-        <is>
-          <t>项目自有图，不用换</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
         <is>
           <t>figs/user/s062.jpg</t>
         </is>
@@ -2530,25 +2326,24 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2.3 气候分析——气温与降水</t>
+          <t>2.6 周边道路分析</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>降水分析图</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr"/>
+          <t>路况分析图</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>项目图（不用换）</t>
+        </is>
+      </c>
       <c r="F64" t="inlineStr">
-        <is>
-          <t>项目自有图，不用换</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
         <is>
           <t>figs/user/s063.jpg</t>
         </is>
@@ -2561,29 +2356,24 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2.3 气候分析——气温与降水</t>
+          <t>2.6 周边道路分析</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>广场花坛与游人</t>
+          <t>场地周边住宅</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>体育公园实景：广场花坛与游人</t>
+          <t>项目图（不用换）</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
-        <is>
-          <t>建议换</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
         <is>
           <t>figs/user/s064.jpg</t>
         </is>
@@ -2596,29 +2386,24 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2.3 气候分析——气温与降水</t>
+          <t>2.6 周边道路分析</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>雨天人群</t>
+          <t>场地原生林地</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>体育公园实景：雨天人群</t>
+          <t>项目图（不用换）</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
-        <is>
-          <t>建议换</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
         <is>
           <t>figs/user/s065.jpg</t>
         </is>
@@ -2631,25 +2416,24 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2.3 气候分析——日照、湿度与雨日</t>
+          <t>2.7 周边交通分析</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>日照时数柱状图</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr"/>
+          <t>交通分析图</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>项目图（不用换）</t>
+        </is>
+      </c>
       <c r="F67" t="inlineStr">
-        <is>
-          <t>项目自有图，不用换</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
         <is>
           <t>figs/user/s066.jpg</t>
         </is>
@@ -2662,25 +2446,24 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2.3 气候分析——日照、湿度与雨日</t>
+          <t>2.7 周边交通分析</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>湿度降水日数折线图</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr"/>
+          <t>公交站点</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>网络照片</t>
+        </is>
+      </c>
       <c r="F68" t="inlineStr">
-        <is>
-          <t>项目自有图，不用换</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
         <is>
           <t>figs/user/s067.jpg</t>
         </is>
@@ -2693,29 +2476,24 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2.3 气候分析——日照、湿度与雨日</t>
+          <t>2.7 周边交通分析</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>儿童戏水、亲水喷泉</t>
+          <t>场地周边住宅</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>体育公园实景：儿童戏水、亲水喷泉</t>
+          <t>项目图（不用换）</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
-        <is>
-          <t>建议换</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
         <is>
           <t>figs/user/s068.jpg</t>
         </is>
@@ -2728,29 +2506,24 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2.3 气候分析——日照、湿度与雨日</t>
+          <t>2.7 周边交通分析</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>廊架休憩空间</t>
+          <t>场地原生林地</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>体育公园实景：廊架休憩空间</t>
+          <t>项目图（不用换）</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
-        <is>
-          <t>建议换</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
         <is>
           <t>figs/user/s069.jpg</t>
         </is>
@@ -2763,25 +2536,24 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2.4 植物分析</t>
+          <t>2.8 周边人行流线分析</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>植物配置分析图</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr"/>
+          <t>人行流线分析图</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>项目图（不用换）</t>
+        </is>
+      </c>
       <c r="F71" t="inlineStr">
-        <is>
-          <t>项目自有图，不用换</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
         <is>
           <t>figs/user/s070.jpg</t>
         </is>
@@ -2794,29 +2566,24 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2.4 植物分析</t>
+          <t>2.8 周边人行流线分析</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>花境、野花组合</t>
+          <t>行人流线</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>体育公园实景：花境、野花组合</t>
+          <t>网络照片</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
-        <is>
-          <t>必换（当前重复）</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
         <is>
           <t>figs/user/s071.jpg</t>
         </is>
@@ -2829,29 +2596,24 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2.4 植物分析</t>
+          <t>2.8 周边人行流线分析</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>花卉植物景观</t>
+          <t>步行街</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>体育公园实景：花卉植物景观</t>
+          <t>网络照片</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
-        <is>
-          <t>必换（当前重复）</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
         <is>
           <t>figs/user/s072.jpg</t>
         </is>
@@ -2864,25 +2626,24 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2.5 历史文化分析</t>
+          <t>2.9 周边用地分析</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>历史文化分析图</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr"/>
+          <t>用地分析图</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>项目图（不用换）</t>
+        </is>
+      </c>
       <c r="F74" t="inlineStr">
-        <is>
-          <t>项目自有图，不用换</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
         <is>
           <t>figs/user/s073.jpg</t>
         </is>
@@ -2895,29 +2656,24 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2.5 历史文化分析</t>
+          <t>2.9 周边用地分析</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>街头老人闲谈</t>
+          <t>场地现状地图</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>体育公园实景：街头老人闲谈</t>
+          <t>项目图（不用换）</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
-        <is>
-          <t>建议换</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
         <is>
           <t>figs/user/s074.jpg</t>
         </is>
@@ -2930,29 +2686,24 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2.5 历史文化分析</t>
+          <t>2.10 地形地貌分析</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>乡土石墙田园</t>
+          <t>场地卫星影像</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>体育公园实景：乡土石墙田园</t>
+          <t>项目图（不用换）</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
-        <is>
-          <t>建议换</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
         <is>
           <t>figs/user/s075.jpg</t>
         </is>
@@ -2965,25 +2716,24 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2.6 周边道路分析</t>
+          <t>2.10 地形地貌分析</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>道路分析图</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr"/>
+          <t>场地局部土坡</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>项目图（不用换）</t>
+        </is>
+      </c>
       <c r="F77" t="inlineStr">
-        <is>
-          <t>项目自有图，不用换</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
         <is>
           <t>figs/user/s076.jpg</t>
         </is>
@@ -2996,25 +2746,24 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2.6 周边道路分析</t>
+          <t>2.10 地形地貌分析</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>路况分析图</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr"/>
+          <t>场地裸土空地</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>项目图（不用换）</t>
+        </is>
+      </c>
       <c r="F78" t="inlineStr">
-        <is>
-          <t>项目自有图，不用换</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
         <is>
           <t>figs/user/s077.jpg</t>
         </is>
@@ -3027,25 +2776,24 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2.6 周边道路分析</t>
+          <t>2.10 地形地貌分析</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>场地周边住宅照片</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr"/>
+          <t>场地周边住宅</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>项目图（不用换）</t>
+        </is>
+      </c>
       <c r="F79" t="inlineStr">
-        <is>
-          <t>项目自有图，不用换</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
         <is>
           <t>figs/user/s078.jpg</t>
         </is>
@@ -3058,25 +2806,24 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2.6 周边道路分析</t>
+          <t>2.11 场地现状分析</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>场地原生林地照片</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr"/>
+          <t>场地现状平面图</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>项目图（不用换）</t>
+        </is>
+      </c>
       <c r="F80" t="inlineStr">
-        <is>
-          <t>项目自有图，不用换</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
         <is>
           <t>figs/user/s079.jpg</t>
         </is>
@@ -3089,25 +2836,24 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2.7 周边交通分析</t>
+          <t>2.11 场地现状分析</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>交通分析图</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr"/>
+          <t>场地裸土空地</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>项目图（不用换）</t>
+        </is>
+      </c>
       <c r="F81" t="inlineStr">
-        <is>
-          <t>项目自有图，不用换</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
         <is>
           <t>figs/user/s080.jpg</t>
         </is>
@@ -3120,29 +2866,24 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2.7 周边交通分析</t>
+          <t>2.11 场地现状分析</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>公交站点人群</t>
+          <t>场地周边住宅</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>体育公园实景：公交站点人群</t>
+          <t>项目图（不用换）</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
-        <is>
-          <t>建议换</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
         <is>
           <t>figs/user/s081.jpg</t>
         </is>
@@ -3155,29 +2896,24 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2.7 周边交通分析</t>
+          <t>2.11 场地现状分析</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>行人步行</t>
+          <t>场地原生林地</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>体育公园实景：行人步行</t>
+          <t>项目图（不用换）</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
-        <is>
-          <t>建议换</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
         <is>
           <t>figs/user/s082.jpg</t>
         </is>
@@ -3190,25 +2926,24 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2.7 周边交通分析</t>
+          <t>2.11 场地现状分析</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>场地周边住宅照片</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr"/>
+          <t>场地局部土坡</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>项目图（不用换）</t>
+        </is>
+      </c>
       <c r="F84" t="inlineStr">
-        <is>
-          <t>项目自有图，不用换</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
         <is>
           <t>figs/user/s083.jpg</t>
         </is>
@@ -3221,25 +2956,24 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2.7 周边交通分析</t>
+          <t>2.11 场地现状分析</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>场地原生林地照片</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr"/>
+          <t>场地卫星影像</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>项目图（不用换）</t>
+        </is>
+      </c>
       <c r="F85" t="inlineStr">
-        <is>
-          <t>项目自有图，不用换</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
         <is>
           <t>figs/user/s084.jpg</t>
         </is>
@@ -3252,25 +2986,24 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2.8 周边人行流线分析</t>
+          <t>2.12 人群结构分析</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>人行流线分析图</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr"/>
+          <t>老年女性</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>网络照片</t>
+        </is>
+      </c>
       <c r="F86" t="inlineStr">
-        <is>
-          <t>项目自有图，不用换</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
         <is>
           <t>figs/user/s085.jpg</t>
         </is>
@@ -3283,29 +3016,24 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2.8 周边人行流线分析</t>
+          <t>2.12 人群结构分析</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>行人步行流线</t>
+          <t>家庭合影</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>体育公园实景：行人步行流线</t>
+          <t>网络照片</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
-        <is>
-          <t>建议换</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
         <is>
           <t>figs/user/s086.jpg</t>
         </is>
@@ -3318,29 +3046,24 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2.8 周边人行流线分析</t>
+          <t>2.12 人群结构分析</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>街道慢行人群</t>
+          <t>少儿棒球</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>体育公园实景：街道慢行人群</t>
+          <t>网络照片</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
-        <is>
-          <t>建议换</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
         <is>
           <t>figs/user/s087.jpg</t>
         </is>
@@ -3353,29 +3076,24 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2.8 周边人行流线分析</t>
+          <t>2.12 人群结构分析</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>绿道骑行</t>
+          <t>山地骑行</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>体育公园实景：绿道骑行</t>
+          <t>网络照片</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
-        <is>
-          <t>必换（当前重复）</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
         <is>
           <t>figs/user/s088.jpg</t>
         </is>
@@ -3388,25 +3106,24 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2.9 周边用地分析</t>
+          <t>2.12 人群结构分析</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>用地分析图</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr"/>
+          <t>台阶人群</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>网络照片</t>
+        </is>
+      </c>
       <c r="F90" t="inlineStr">
-        <is>
-          <t>项目自有图，不用换</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
         <is>
           <t>figs/user/s089.jpg</t>
         </is>
@@ -3419,25 +3136,24 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2.9 周边用地分析</t>
+          <t>2.12 人群结构分析</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>场地现状地图</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr"/>
+          <t>人群来源饼图</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>项目图（不用换）</t>
+        </is>
+      </c>
       <c r="F91" t="inlineStr">
-        <is>
-          <t>项目自有图，不用换</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
         <is>
           <t>figs/user/s090.jpg</t>
         </is>
@@ -3450,29 +3166,24 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2.9 周边用地分析</t>
+          <t>2.12 人群结构分析</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>公交车站</t>
+          <t>年龄构成饼图</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>体育公园实景：公交车站</t>
+          <t>项目图（不用换）</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
-        <is>
-          <t>建议换</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
         <is>
           <t>figs/user/s091.jpg</t>
         </is>
@@ -3485,25 +3196,24 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2.10 地形地貌分析</t>
+          <t>2.12 人群结构分析</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>场地卫星影像</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr"/>
+          <t>性别构成饼图</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>项目图（不用换）</t>
+        </is>
+      </c>
       <c r="F93" t="inlineStr">
-        <is>
-          <t>项目自有图，不用换</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
         <is>
           <t>figs/user/s092.jpg</t>
         </is>
@@ -3516,25 +3226,24 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2.10 地形地貌分析</t>
+          <t>2.13 主要人群需求分析</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>场地局部土坡照片</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr"/>
+          <t>街道慢行</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>网络照片</t>
+        </is>
+      </c>
       <c r="F94" t="inlineStr">
-        <is>
-          <t>项目自有图，不用换</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
         <is>
           <t>figs/user/s093.jpg</t>
         </is>
@@ -3547,25 +3256,24 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2.10 地形地貌分析</t>
+          <t>2.13 主要人群需求分析</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>场地裸土空地照片</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr"/>
+          <t>滨水草地放风筝</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>网络照片</t>
+        </is>
+      </c>
       <c r="F95" t="inlineStr">
-        <is>
-          <t>项目自有图，不用换</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
         <is>
           <t>figs/user/s094.jpg</t>
         </is>
@@ -3578,25 +3286,24 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2.10 地形地貌分析</t>
+          <t>2.13 主要人群需求分析</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>场地周边住宅照片</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr"/>
+          <t>老年人</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>网络照片</t>
+        </is>
+      </c>
       <c r="F96" t="inlineStr">
-        <is>
-          <t>项目自有图，不用换</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
         <is>
           <t>figs/user/s095.jpg</t>
         </is>
@@ -3609,29 +3316,24 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2.10 地形地貌分析</t>
+          <t>2.13 主要人群需求分析</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>广场台阶人群</t>
+          <t>器械体操</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>体育公园实景：广场台阶人群</t>
+          <t>网络照片</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
-        <is>
-          <t>建议换</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
         <is>
           <t>figs/user/s096.jpg</t>
         </is>
@@ -3644,25 +3346,24 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2.11 场地现状分析</t>
+          <t>2.13 主要人群需求分析</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>场地现状平面图</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr"/>
+          <t>街头活动人群</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>网络照片</t>
+        </is>
+      </c>
       <c r="F98" t="inlineStr">
-        <is>
-          <t>项目自有图，不用换</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
         <is>
           <t>figs/user/s097.jpg</t>
         </is>
@@ -3675,25 +3376,24 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2.11 场地现状分析</t>
+          <t>2.13 主要人群需求分析</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>场地裸土空地照片</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr"/>
+          <t>滑板运动</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>网络照片</t>
+        </is>
+      </c>
       <c r="F99" t="inlineStr">
-        <is>
-          <t>项目自有图，不用换</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
         <is>
           <t>figs/user/s098.jpg</t>
         </is>
@@ -3706,25 +3406,24 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2.11 场地现状分析</t>
+          <t>2.13 主要人群需求分析</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>场地周边住宅照片</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr"/>
+          <t>雨天人群</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>网络照片</t>
+        </is>
+      </c>
       <c r="F100" t="inlineStr">
-        <is>
-          <t>项目自有图，不用换</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
         <is>
           <t>figs/user/s099.jpg</t>
         </is>
@@ -3737,25 +3436,24 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2.11 场地现状分析</t>
+          <t>2.13 主要人群需求分析</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>场地原生林地照片</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr"/>
+          <t>轮椅运动</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>网络照片</t>
+        </is>
+      </c>
       <c r="F101" t="inlineStr">
-        <is>
-          <t>项目自有图，不用换</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
         <is>
           <t>figs/user/s100.jpg</t>
         </is>
@@ -3768,25 +3466,24 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2.11 场地现状分析</t>
+          <t>2.13 主要人群需求分析——调研数据</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>场地局部土坡照片</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr"/>
+          <t>活动类型饼图</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>项目图（不用换）</t>
+        </is>
+      </c>
       <c r="F102" t="inlineStr">
-        <is>
-          <t>项目自有图，不用换</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
         <is>
           <t>figs/user/s101.jpg</t>
         </is>
@@ -3799,25 +3496,24 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2.11 场地现状分析</t>
+          <t>2.13 主要人群需求分析——调研数据</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>场地卫星影像</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr"/>
+          <t>活动时段饼图</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>项目图（不用换）</t>
+        </is>
+      </c>
       <c r="F103" t="inlineStr">
-        <is>
-          <t>项目自有图，不用换</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
         <is>
           <t>figs/user/s102.jpg</t>
         </is>
@@ -3830,29 +3526,24 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2.12 人群结构分析</t>
+          <t>2.14 光照分析</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>老人长椅社交</t>
+          <t>日照分析图</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>体育公园实景：老人长椅社交</t>
+          <t>项目图（不用换）</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
-        <is>
-          <t>建议换</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
         <is>
           <t>figs/user/s103.jpg</t>
         </is>
@@ -3865,29 +3556,24 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2.12 人群结构分析</t>
+          <t>2.14 光照分析</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>家庭合影</t>
+          <t>光照分析图</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>体育公园实景：家庭合影</t>
+          <t>项目图（不用换）</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
-        <is>
-          <t>建议换</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
         <is>
           <t>figs/user/s104.jpg</t>
         </is>
@@ -3900,29 +3586,24 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2.12 人群结构分析</t>
+          <t>2.15 SWOT分析</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>滑板极限运动场</t>
+          <t>场地卫星影像</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>体育公园实景：滑板极限运动场</t>
+          <t>项目图（不用换）</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
-        <is>
-          <t>必换（当前重复）</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
         <is>
           <t>figs/user/s105.jpg</t>
         </is>
@@ -3935,29 +3616,24 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2.12 人群结构分析</t>
+          <t>2.15 SWOT分析</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>健身运动</t>
+          <t>场地裸土空地</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>体育公园实景：健身运动</t>
+          <t>项目图（不用换）</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
-        <is>
-          <t>必换（当前重复）</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
         <is>
           <t>figs/user/s106.jpg</t>
         </is>
@@ -3970,29 +3646,24 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2.12 人群结构分析</t>
+          <t>2.15 SWOT分析</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>大草坪人群活动</t>
+          <t>场地现状地图</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>体育公园实景：大草坪人群活动</t>
+          <t>项目图（不用换）</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
-        <is>
-          <t>必换（当前重复）</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
         <is>
           <t>figs/user/s107.jpg</t>
         </is>
@@ -4005,25 +3676,24 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2.12 人群结构分析</t>
+          <t>2.15 SWOT分析</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>人群来源饼图</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr"/>
+          <t>场地局部土坡</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>项目图（不用换）</t>
+        </is>
+      </c>
       <c r="F109" t="inlineStr">
-        <is>
-          <t>项目自有图，不用换</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
         <is>
           <t>figs/user/s108.jpg</t>
         </is>
@@ -4036,25 +3706,24 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2.12 人群结构分析</t>
+          <t>2.16 问题梳理</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>年龄构成饼图</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr"/>
+          <t>场地原生林地</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>项目图（不用换）</t>
+        </is>
+      </c>
       <c r="F110" t="inlineStr">
-        <is>
-          <t>项目自有图，不用换</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
         <is>
           <t>figs/user/s109.jpg</t>
         </is>
@@ -4067,25 +3736,24 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2.12 人群结构分析</t>
+          <t>2.16 问题梳理</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>性别构成饼图</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr"/>
+          <t>场地周边住宅</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>项目图（不用换）</t>
+        </is>
+      </c>
       <c r="F111" t="inlineStr">
-        <is>
-          <t>项目自有图，不用换</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
         <is>
           <t>figs/user/s110.jpg</t>
         </is>
@@ -4098,29 +3766,24 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2.13 主要人群需求分析</t>
+          <t>2.16 问题梳理</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>社区骑行活动人群</t>
+          <t>场地局部土坡</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>体育公园实景：社区骑行活动人群</t>
+          <t>项目图（不用换）</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
-        <is>
-          <t>必换（当前重复）</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
         <is>
           <t>figs/user/s111.jpg</t>
         </is>
@@ -4133,29 +3796,24 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2.13 主要人群需求分析</t>
+          <t>03 场地规划分析</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>草坪亲子活动（放风筝、野餐）</t>
+          <t>校园球场活动</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>体育公园实景：草坪亲子活动（放风筝、野餐）</t>
+          <t>网络照片</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
-        <is>
-          <t>必换（当前重复）</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
         <is>
           <t>figs/user/s112.jpg</t>
         </is>
@@ -4168,29 +3826,24 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2.13 主要人群需求分析</t>
+          <t>3.1 设计目标</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>老人聚会</t>
+          <t>田园草垛</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>体育公园实景：老人聚会</t>
+          <t>网络照片</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
-        <is>
-          <t>建议换</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
         <is>
           <t>figs/user/s113.jpg</t>
         </is>
@@ -4203,29 +3856,24 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2.13 主要人群需求分析</t>
+          <t>3.1 设计目标</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>户外单杠健身器械</t>
+          <t>网球比赛</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>体育公园实景：户外单杠健身器械</t>
+          <t>网络照片</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
-        <is>
-          <t>必换（当前重复）</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
         <is>
           <t>figs/user/s114.jpg</t>
         </is>
@@ -4238,29 +3886,24 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2.13 主要人群需求分析</t>
+          <t>3.1 设计目标</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>篮球场比赛</t>
+          <t>环岛与绿地航拍</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>体育公园实景：篮球场比赛</t>
+          <t>网络照片</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
-        <is>
-          <t>必换（当前重复）</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
         <is>
           <t>figs/user/s115.jpg</t>
         </is>
@@ -4273,29 +3916,24 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2.13 主要人群需求分析</t>
+          <t>3.1 设计目标</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>网球运动员</t>
+          <t>场地卫星影像</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>体育公园实景：网球运动员</t>
+          <t>项目图（不用换）</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
-        <is>
-          <t>必换（当前重复）</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
         <is>
           <t>figs/user/s116.jpg</t>
         </is>
@@ -4308,29 +3946,24 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2.13 主要人群需求分析</t>
+          <t>3.2 设计原则</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>滑板极限运动场</t>
+          <t>儿童坐长椅</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>体育公园实景：滑板极限运动场</t>
+          <t>网络照片</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
-        <is>
-          <t>必换（当前重复）</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
         <is>
           <t>figs/user/s117.jpg</t>
         </is>
@@ -4343,29 +3976,24 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2.13 主要人群需求分析</t>
+          <t>3.2 设计原则</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>轮椅运动、无障碍运动</t>
+          <t>城市广场</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>体育公园实景：轮椅运动、无障碍运动</t>
+          <t>网络照片</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
-        <is>
-          <t>必换（当前重复）</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
         <is>
           <t>figs/user/s118.jpg</t>
         </is>
@@ -4378,29 +4006,24 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2.13 主要人群需求分析</t>
+          <t>3.2 设计原则</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>老年人肖像</t>
+          <t>花境地被</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>体育公园实景：老年人肖像</t>
+          <t>网络照片</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
-        <is>
-          <t>建议换</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
         <is>
           <t>figs/user/s119.jpg</t>
         </is>
@@ -4413,29 +4036,24 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2.13 主要人群需求分析</t>
+          <t>3.2 设计原则</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>老人赏花</t>
+          <t>滨水桥体</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>体育公园实景：老人赏花</t>
+          <t>网络照片</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
-        <is>
-          <t>建议换</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
         <is>
           <t>figs/user/s120.jpg</t>
         </is>
@@ -4448,29 +4066,24 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2.13 主要人群需求分析</t>
+          <t>3.3 设计构思</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>广场人群</t>
+          <t>场地卫星影像</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>体育公园实景：广场人群</t>
+          <t>项目图（不用换）</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
-        <is>
-          <t>建议换</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
         <is>
           <t>figs/user/s121.jpg</t>
         </is>
@@ -4483,29 +4096,24 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2.13 主要人群需求分析</t>
+          <t>3.3 设计构思</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>少儿球类训练</t>
+          <t>平衡木体操</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>体育公园实景：少儿球类训练</t>
+          <t>网络照片</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
-        <is>
-          <t>必换（当前重复）</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
         <is>
           <t>figs/user/s122.jpg</t>
         </is>
@@ -4518,25 +4126,24 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2.13 主要人群需求分析——调研数据</t>
+          <t>3.3 设计构思</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>活动类型饼图</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr"/>
+          <t>公园长椅草坪</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>网络照片</t>
+        </is>
+      </c>
       <c r="F124" t="inlineStr">
-        <is>
-          <t>项目自有图，不用换</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
         <is>
           <t>figs/user/s123.jpg</t>
         </is>
@@ -4549,25 +4156,24 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2.13 主要人群需求分析——调研数据</t>
+          <t>3.3 设计构思</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>活动时段饼图</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr"/>
+          <t>喷泉水景</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>网络照片</t>
+        </is>
+      </c>
       <c r="F125" t="inlineStr">
-        <is>
-          <t>项目自有图，不用换</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
         <is>
           <t>figs/user/s124.jpg</t>
         </is>
@@ -4580,25 +4186,24 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2.14 光照分析</t>
+          <t>3.4 设计策略——策略框架</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>日照分析图1</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr"/>
+          <t>设计策略框架图</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>项目图（不用换）</t>
+        </is>
+      </c>
       <c r="F126" t="inlineStr">
-        <is>
-          <t>项目自有图，不用换</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
         <is>
           <t>figs/user/s125.jpg</t>
         </is>
@@ -4611,25 +4216,24 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2.14 光照分析</t>
+          <t>3.4 设计策略——策略框架</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>日照分析图2</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr"/>
+          <t>双人骑行</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>网络照片</t>
+        </is>
+      </c>
       <c r="F127" t="inlineStr">
-        <is>
-          <t>项目自有图，不用换</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
         <is>
           <t>figs/user/s126.jpg</t>
         </is>
@@ -4642,29 +4246,24 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2.14 光照分析</t>
+          <t>3.4 设计策略——策略框架</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>阳光草坪休闲人群</t>
+          <t>公园标识导览牌</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>体育公园实景：阳光草坪休闲人群</t>
+          <t>网络照片</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
-        <is>
-          <t>必换（当前重复）</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
         <is>
           <t>figs/user/s127.jpg</t>
         </is>
@@ -4677,29 +4276,24 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2.14 光照分析</t>
+          <t>3.4 设计策略——策略框架</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>滨水林荫座椅</t>
+          <t>水岸构筑</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>体育公园实景：滨水林荫座椅</t>
+          <t>网络照片</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
-        <is>
-          <t>必换（当前重复）</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
         <is>
           <t>figs/user/s128.jpg</t>
         </is>
@@ -4712,29 +4306,24 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2.14 光照分析</t>
+          <t>3.4 设计策略——回应2.16问题</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>花卉植物景观</t>
+          <t>街道人流航拍</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>体育公园实景：花卉植物景观</t>
+          <t>网络照片</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
-        <is>
-          <t>必换（当前重复）</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
         <is>
           <t>figs/user/s129.jpg</t>
         </is>
@@ -4747,25 +4336,24 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2.15 SWOT分析</t>
+          <t>3.4 设计策略——回应2.16问题</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>场地卫星影像</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr"/>
+          <t>街头独轮车</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>网络照片</t>
+        </is>
+      </c>
       <c r="F131" t="inlineStr">
-        <is>
-          <t>项目自有图，不用换</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
         <is>
           <t>figs/user/s130.jpg</t>
         </is>
@@ -4778,25 +4366,24 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2.15 SWOT分析</t>
+          <t>3.4 设计策略——回应2.16问题</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>场地裸土空地照片</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr"/>
+          <t>自行车停放与围栏</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>网络照片</t>
+        </is>
+      </c>
       <c r="F132" t="inlineStr">
-        <is>
-          <t>项目自有图，不用换</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
         <is>
           <t>figs/user/s131.jpg</t>
         </is>
@@ -4809,25 +4396,24 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2.15 SWOT分析</t>
+          <t>3.4 设计策略——回应2.16问题</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>场地现状地图</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr"/>
+          <t>乡土石墙</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>网络照片</t>
+        </is>
+      </c>
       <c r="F133" t="inlineStr">
-        <is>
-          <t>项目自有图，不用换</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
         <is>
           <t>figs/user/s132.jpg</t>
         </is>
@@ -4840,25 +4426,24 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2.15 SWOT分析</t>
+          <t>3.5 设计成果</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>场地局部土坡照片</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr"/>
+          <t>城市街道</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>网络照片</t>
+        </is>
+      </c>
       <c r="F134" t="inlineStr">
-        <is>
-          <t>项目自有图，不用换</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
         <is>
           <t>figs/user/s133.jpg</t>
         </is>
@@ -4871,25 +4456,24 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2.16 问题梳理</t>
+          <t>3.5 设计成果</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>场地原生林地照片</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr"/>
+          <t>林荫道路</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>网络照片</t>
+        </is>
+      </c>
       <c r="F135" t="inlineStr">
-        <is>
-          <t>项目自有图，不用换</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
         <is>
           <t>figs/user/s134.jpg</t>
         </is>
@@ -4902,25 +4486,24 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2.16 问题梳理</t>
+          <t>3.5 设计成果</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>场地周边住宅照片</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr"/>
+          <t>植物配置分析图</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>项目图（不用换）</t>
+        </is>
+      </c>
       <c r="F136" t="inlineStr">
-        <is>
-          <t>项目自有图，不用换</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
         <is>
           <t>figs/user/s135.jpg</t>
         </is>
@@ -4933,25 +4516,24 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2.16 问题梳理</t>
+          <t>3.5 设计成果</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>场地局部土坡照片</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr"/>
+          <t>场地现状平面图</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>项目图（不用换）</t>
+        </is>
+      </c>
       <c r="F137" t="inlineStr">
-        <is>
-          <t>项目自有图，不用换</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
         <is>
           <t>figs/user/s136.jpg</t>
         </is>
@@ -4964,11 +4546,11 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>03 场地规划分析</t>
+          <t>3.7 参考文献（2/2）</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -4978,1222 +4560,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>体育公园实景：网球场打球</t>
+          <t>网络照片</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>必换（当前重复）</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
           <t>figs/user/s137.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>s138</t>
-        </is>
-      </c>
-      <c r="B139" t="n">
-        <v>35</v>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>03 场地规划分析</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>公园标识导览牌</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>体育公园实景：公园标识导览牌</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>建议换</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>figs/user/s138.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>s139</t>
-        </is>
-      </c>
-      <c r="B140" t="n">
-        <v>36</v>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>3.1 设计目标</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>公园湖岸生态水景</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>体育公园实景：公园湖岸生态水景</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>必换（当前重复）</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>figs/user/s139.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>s140</t>
-        </is>
-      </c>
-      <c r="B141" t="n">
-        <v>36</v>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>3.1 设计目标</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>花境、野花组合</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>体育公园实景：花境、野花组合</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>必换（当前重复）</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>figs/user/s140.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>s141</t>
-        </is>
-      </c>
-      <c r="B142" t="n">
-        <v>36</v>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>3.1 设计目标</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>篮球场比赛</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>体育公园实景：篮球场比赛</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>必换（当前重复）</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>figs/user/s141.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>s142</t>
-        </is>
-      </c>
-      <c r="B143" t="n">
-        <v>36</v>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>3.1 设计目标</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>网球运动员</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>体育公园实景：网球运动员</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>必换（当前重复）</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>figs/user/s142.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>s143</t>
-        </is>
-      </c>
-      <c r="B144" t="n">
-        <v>36</v>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>3.1 设计目标</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>城市新城航拍</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>体育公园实景：城市新城航拍</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>必换（当前重复）</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>figs/user/s143.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>s144</t>
-        </is>
-      </c>
-      <c r="B145" t="n">
-        <v>36</v>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>3.1 设计目标</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>公园标识导览牌</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>体育公园实景：公园标识导览牌</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>必换（当前重复）</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>figs/user/s144.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>s145</t>
-        </is>
-      </c>
-      <c r="B146" t="n">
-        <v>36</v>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>3.1 设计目标</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>场地卫星影像</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr"/>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>项目自有图，不用换</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>figs/user/s145.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>s146</t>
-        </is>
-      </c>
-      <c r="B147" t="n">
-        <v>36</v>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>3.1 设计目标</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>乡土石墙田园</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>体育公园实景：乡土石墙田园</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>必换（当前重复）</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>figs/user/s146.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>s147</t>
-        </is>
-      </c>
-      <c r="B148" t="n">
-        <v>37</v>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>3.2 设计原则</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>儿童秋千游乐设施</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>体育公园实景：儿童秋千游乐设施</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>必换（当前重复）</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>figs/user/s147.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>s148</t>
-        </is>
-      </c>
-      <c r="B149" t="n">
-        <v>37</v>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>3.2 设计原则</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>轮椅运动、无障碍运动</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>体育公园实景：轮椅运动、无障碍运动</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>必换（当前重复）</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>figs/user/s148.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>s149</t>
-        </is>
-      </c>
-      <c r="B150" t="n">
-        <v>37</v>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>3.2 设计原则</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>城市广场入口</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>体育公园实景：城市广场入口</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>必换（当前重复）</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>figs/user/s149.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>s150</t>
-        </is>
-      </c>
-      <c r="B151" t="n">
-        <v>37</v>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>3.2 设计原则</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>社区骑行活动人群</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>体育公园实景：社区骑行活动人群</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>必换（当前重复）</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>figs/user/s150.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>s151</t>
-        </is>
-      </c>
-      <c r="B152" t="n">
-        <v>37</v>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>3.2 设计原则</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>乡土石墙田园</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>体育公园实景：乡土石墙田园</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>必换（当前重复）</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>figs/user/s151.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>s152</t>
-        </is>
-      </c>
-      <c r="B153" t="n">
-        <v>37</v>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>3.2 设计原则</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>街头老人闲谈</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>体育公园实景：街头老人闲谈</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>必换（当前重复）</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>figs/user/s152.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>s153</t>
-        </is>
-      </c>
-      <c r="B154" t="n">
-        <v>37</v>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>3.2 设计原则</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>公园湖岸生态水景</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>体育公园实景：公园湖岸生态水景</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>必换（当前重复）</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>figs/user/s153.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>s154</t>
-        </is>
-      </c>
-      <c r="B155" t="n">
-        <v>37</v>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>3.2 设计原则</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>花卉植物景观</t>
-        </is>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>体育公园实景：花卉植物景观</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>必换（当前重复）</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>figs/user/s154.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>s155</t>
-        </is>
-      </c>
-      <c r="B156" t="n">
-        <v>38</v>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>3.3 设计构思</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>场地卫星影像</t>
-        </is>
-      </c>
-      <c r="E156" t="inlineStr"/>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>项目自有图，不用换</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>figs/user/s155.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>s156</t>
-        </is>
-      </c>
-      <c r="B157" t="n">
-        <v>38</v>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>3.3 设计构思</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>户外单杠健身器械</t>
-        </is>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>体育公园实景：户外单杠健身器械</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>必换（当前重复）</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>figs/user/s156.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>s157</t>
-        </is>
-      </c>
-      <c r="B158" t="n">
-        <v>38</v>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>3.3 设计构思</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>滨水林荫座椅</t>
-        </is>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>体育公园实景：滨水林荫座椅</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>必换（当前重复）</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>figs/user/s157.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>s158</t>
-        </is>
-      </c>
-      <c r="B159" t="n">
-        <v>38</v>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>3.3 设计构思</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>儿童秋千游乐设施</t>
-        </is>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>体育公园实景：儿童秋千游乐设施</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>必换（当前重复）</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>figs/user/s158.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>s159</t>
-        </is>
-      </c>
-      <c r="B160" t="n">
-        <v>39</v>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>3.4 设计策略——策略框架</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>设计策略框架图</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr"/>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>项目自有图，不用换</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>figs/user/s159.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>s160</t>
-        </is>
-      </c>
-      <c r="B161" t="n">
-        <v>39</v>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>3.4 设计策略——策略框架</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>网球场打球</t>
-        </is>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>体育公园实景：网球场打球</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>必换（当前重复）</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>figs/user/s160.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>s161</t>
-        </is>
-      </c>
-      <c r="B162" t="n">
-        <v>39</v>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>3.4 设计策略——策略框架</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>公园标识导览牌</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>体育公园实景：公园标识导览牌</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>必换（当前重复）</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>figs/user/s161.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>s162</t>
-        </is>
-      </c>
-      <c r="B163" t="n">
-        <v>39</v>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>3.4 设计策略——策略框架</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>花卉植物景观</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>体育公园实景：花卉植物景观</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>必换（当前重复）</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>figs/user/s162.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>s163</t>
-        </is>
-      </c>
-      <c r="B164" t="n">
-        <v>40</v>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>3.4 设计策略——回应2.16问题</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>公园道路航拍</t>
-        </is>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>体育公园实景：公园道路航拍</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>必换（当前重复）</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>figs/user/s163.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>s164</t>
-        </is>
-      </c>
-      <c r="B165" t="n">
-        <v>40</v>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>3.4 设计策略——回应2.16问题</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>草坪亲子活动（放风筝、野餐）</t>
-        </is>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>体育公园实景：草坪亲子活动（放风筝、野餐）</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>必换（当前重复）</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>figs/user/s164.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>s165</t>
-        </is>
-      </c>
-      <c r="B166" t="n">
-        <v>40</v>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>3.4 设计策略——回应2.16问题</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>篮球场比赛</t>
-        </is>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>体育公园实景：篮球场比赛</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>必换（当前重复）</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>figs/user/s165.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>s166</t>
-        </is>
-      </c>
-      <c r="B167" t="n">
-        <v>40</v>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>3.4 设计策略——回应2.16问题</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>花境、野花组合</t>
-        </is>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>体育公园实景：花境、野花组合</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>必换（当前重复）</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>figs/user/s166.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>s167</t>
-        </is>
-      </c>
-      <c r="B168" t="n">
-        <v>41</v>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>3.5 设计成果</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>公园道路航拍</t>
-        </is>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>体育公园实景：公园道路航拍</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>必换（当前重复）</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>figs/user/s167.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>s168</t>
-        </is>
-      </c>
-      <c r="B169" t="n">
-        <v>41</v>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>3.5 设计成果</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>篮球场比赛</t>
-        </is>
-      </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>体育公园实景：篮球场比赛</t>
-        </is>
-      </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>必换（当前重复）</t>
-        </is>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>figs/user/s168.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>s169</t>
-        </is>
-      </c>
-      <c r="B170" t="n">
-        <v>41</v>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>3.5 设计成果</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>植物配置分析图</t>
-        </is>
-      </c>
-      <c r="E170" t="inlineStr"/>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>项目自有图，不用换</t>
-        </is>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>figs/user/s169.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>s170</t>
-        </is>
-      </c>
-      <c r="B171" t="n">
-        <v>41</v>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>3.5 设计成果</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>场地现状平面图</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr"/>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>项目自有图，不用换</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>figs/user/s170.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>s171</t>
-        </is>
-      </c>
-      <c r="B172" t="n">
-        <v>44</v>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>3.7 参考文献（2/2）</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>公园湖岸生态水景</t>
-        </is>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>体育公园实景：公园湖岸生态水景</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>必换（当前重复）</t>
-        </is>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>figs/user/s171.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>s172</t>
-        </is>
-      </c>
-      <c r="B173" t="n">
-        <v>44</v>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>3.7 参考文献（2/2）</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>儿童秋千游乐设施</t>
-        </is>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>体育公园实景：儿童秋千游乐设施</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>必换（当前重复）</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>figs/user/s172.jpg</t>
         </is>
       </c>
     </row>
@@ -6217,35 +4589,35 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>1. 按“编号”把找到的图片改名放到 pptx_build/figs/user/ 目录，例如 s012.jpg（jpg 或 png 均可）。</t>
+          <t>1. 全稿共 137 个图位，无一张图片重复使用。</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2. 图片不需要裁切，脚本按原始比例放置；竖版位置尽量给竖图，横版位置给横图。</t>
+          <t>2. 其中 66 张为网络公开照片（已转黑白），71 张为项目自有分析图、场地照片与案例照片。</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3. 优先补“必换”的编号，其次“建议换”。项目自有图（卫星图、分析图、案例照片）不用换。</t>
+          <t>3. 想换某个位置的图：按编号命名（如 s012.jpg）放到 pptx_build/figs/user/ 目录。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>4. 放好后在 pptx_build 目录运行 node gen_pptx.js 重新生成。</t>
+          <t>4. 放好后在 pptx_build 目录运行 node gen_pptx.js 重新生成，脚本自动替换。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5. 用户图片不会被自动转黑白，需要统一色调可自行处理后再放入。</t>
+          <t>5. 图片按原始比例放置，不裁切不拉伸；竖版位置建议给竖图。</t>
         </is>
       </c>
     </row>
